--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -1083,7 +1083,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Role must be faculty, gtf, or la." type="list">
+    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Role must be faculty, gtf, or la." type="list">
       <formula1>"faculty,gtf,la"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2679,16 +2679,16 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="B2:B400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B2:B400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Office hours are Monday to Friday." type="list">
       <formula1>"Monday,Tuesday,Wednesday,Thursday,Friday"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Use in-person or online. Blank means in-person." type="list">
       <formula1>"in-person,online"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Use yes or no. Blank means yes." type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Pick a name from the people sheet. Add them there first if they are new." type="list">
+    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Pick a name from the people sheet. Add them there first if they are new." type="list">
       <formula1>PeopleNames</formula1>
     </dataValidation>
   </dataValidations>
@@ -2762,10 +2762,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Use cancelled or added." type="list">
       <formula1>"cancelled,added"</formula1>
     </dataValidation>
-    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Pick a name from the people sheet." type="list">
       <formula1>PeopleNames</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1078,6 +1078,54 @@
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>gtf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>DEMO One</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>DEMO - example (AV 141)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>faculty</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>DEMO Two</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>DEMO - example (Scott)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>la</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1180,7 +1228,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1203,7 +1250,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1226,7 +1272,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1249,7 +1294,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1272,7 +1316,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1295,7 +1338,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1318,7 +1360,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1341,7 +1382,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1364,7 +1404,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1387,7 +1426,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1410,7 +1448,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1433,7 +1470,6 @@
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1456,7 +1492,6 @@
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1479,7 +1514,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1502,7 +1536,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1525,7 +1558,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1548,7 +1580,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1571,7 +1602,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1594,7 +1624,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1617,7 +1646,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1640,7 +1668,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1663,7 +1690,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1686,7 +1712,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1709,7 +1734,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1732,7 +1756,6 @@
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1755,7 +1778,6 @@
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1778,7 +1800,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1801,7 +1822,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1824,7 +1844,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1847,7 +1866,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1870,7 +1888,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1893,7 +1910,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1916,7 +1932,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1939,7 +1954,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1962,7 +1976,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1985,7 +1998,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2008,7 +2020,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2031,7 +2042,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2054,7 +2064,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2077,7 +2086,6 @@
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2100,7 +2108,6 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2123,7 +2130,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2146,7 +2152,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2169,7 +2174,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2192,7 +2196,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2215,7 +2218,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2238,7 +2240,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2261,7 +2262,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2284,7 +2284,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2307,7 +2306,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2330,7 +2328,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2353,7 +2350,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2376,7 +2372,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2399,7 +2394,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2422,7 +2416,6 @@
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2445,7 +2438,6 @@
           <t>6:00 PM</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2468,7 +2460,6 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2491,7 +2482,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2514,7 +2504,6 @@
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2537,7 +2526,6 @@
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2560,7 +2548,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2583,7 +2570,6 @@
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2606,7 +2592,6 @@
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2629,7 +2614,6 @@
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2652,7 +2636,6 @@
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2675,7 +2658,123 @@
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>DEMO One</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>in-person</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>AV C141</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>DEMO Two</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>in-person</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Scott Engineering</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>DEMO One</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>in-person</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>AV C141</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -2757,9 +2856,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Use cancelled or added." type="list">
@@ -2779,7 +2876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2866,7 +2963,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>AV C147</t>
+          <t>AV C144</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2975,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>AV C147</t>
+          <t>AV C144</t>
         </is>
       </c>
     </row>
@@ -2925,6 +3022,18 @@
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>room_order</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>AV C144; AV C141; Scott Engineering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2950,9 +3059,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2967,9 +3074,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -3019,9 +3124,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -3029,9 +3132,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -3088,9 +3189,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -3119,9 +3218,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
@@ -3129,9 +3226,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -2801,7 +2801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2856,7 +2856,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Use cancelled or added." type="list">
@@ -2876,7 +2875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3032,6 +3031,18 @@
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>AV C144; AV C141; Scott Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>course_implies</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ENGR 111 -&gt; ENGR 123</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3070,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3074,7 +3084,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -3124,7 +3133,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -3132,7 +3140,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -3189,7 +3196,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
@@ -3218,7 +3224,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
@@ -3226,7 +3231,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1448,6 +1448,16 @@
           <t>4:00 PM</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/meet/245625331850941?p=iV1rimtH5TCpcr9fc3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1694,7 +1704,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Prof Scheller</t>
+          <t>Sophie DeMatteo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1710,13 +1720,23 @@
       <c r="D24" s="4" t="inlineStr">
         <is>
           <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/meet/235485688487049?p=yJrCzr8Ds8hzdA8dh2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sophie DeMatteo</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1726,12 +1746,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
     </row>
@@ -1748,41 +1768,41 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Owen Myers</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Owen Myers</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1792,19 +1812,19 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Kacey Hoang</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1826,7 +1846,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kacey Hoang</t>
+          <t>Dr. Dan</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1836,19 +1856,19 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dr. Dan</t>
+          <t>Lauren Watts</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1870,7 +1890,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lauren Watts</t>
+          <t>Winnie</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1892,7 +1912,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Winnie</t>
+          <t>Dr. Yume</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1902,19 +1922,19 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dr. Yume</t>
+          <t>River Wysock</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1936,7 +1956,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>River Wysock</t>
+          <t>DrT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1946,19 +1966,19 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DrT</t>
+          <t>Joseph Quiroz Hernandez</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1980,7 +2000,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Joseph Quiroz Hernandez</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1990,19 +2010,19 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>DrT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2024,7 +2044,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DrT</t>
+          <t>Hannah Gruber</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2046,7 +2066,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hannah Gruber</t>
+          <t>Sumaiya</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2056,19 +2076,19 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sumaiya</t>
+          <t>Jordy Medina Valverde</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2078,41 +2098,41 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jordy Medina Valverde</t>
+          <t>Parker Bjick</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Parker Bjick</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2134,7 +2154,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Austin Monroe</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2144,19 +2164,19 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Austin Monroe</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2178,7 +2198,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2188,19 +2208,19 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Tia Fountain</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2222,7 +2242,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tia Fountain</t>
+          <t>Dr. Harvey</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2232,19 +2252,19 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dr. Harvey</t>
+          <t>Sarah Goudjil</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2266,7 +2286,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sarah Goudjil</t>
+          <t>Dr. Harvey</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2276,19 +2296,19 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dr. Harvey</t>
+          <t>Prof Scheller</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2310,7 +2330,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Prof Scheller</t>
+          <t>Tucker Cullen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2326,13 +2346,23 @@
       <c r="D52" s="4" t="inlineStr">
         <is>
           <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/l/message/19:42625ed077084999881c0275e689deec@thread.v2/1787625651798?context=%7B%22contextType%22%3A%22chat%22%7D</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tucker Cullen</t>
+          <t>Julie Rickerd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2342,19 +2372,19 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Julie Rickerd</t>
+          <t>Prof Scheller</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2376,7 +2406,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Prof Scheller</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2386,12 +2416,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
     </row>
@@ -2408,19 +2438,19 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Sylvia Ingegneri</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2430,41 +2460,41 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sylvia Ingegneri</t>
+          <t>Mia White</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mia White</t>
+          <t>Winnie</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2486,7 +2516,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Winnie</t>
+          <t>Jady Sharp</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2496,19 +2526,19 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jady Sharp</t>
+          <t>Caleb Adams</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2518,19 +2548,19 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Caleb Adams</t>
+          <t>Winnie</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2552,7 +2582,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Winnie</t>
+          <t>Landon Gagliostro</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2562,19 +2592,19 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Landon Gagliostro</t>
+          <t>Olivia Kalinowski</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2584,19 +2614,29 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/l/message/19:42625ed077084999881c0275e689deec@thread.v2/1787623810109?context=%7B%22contextType%22%3A%22chat%22%7D</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Olivia Kalinowski</t>
+          <t>Tito Salcido Rascon</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2606,19 +2646,19 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tito Salcido Rascon</t>
+          <t>Thomas Miller</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2628,41 +2668,58 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Thomas Miller</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>10:00 AM</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>DEMO One</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>6:30 PM</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>in-person</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>AV C141</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>DEMO One</t>
+          <t>DEMO Two</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2672,7 +2729,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>6:30 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2687,7 +2744,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>AV C141</t>
+          <t>Scott Engineering</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2701,24 +2758,24 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>DEMO Two</t>
+          <t>DEMO One</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
           <t>in-person</t>
@@ -2726,51 +2783,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Scott Engineering</t>
+          <t>AV C141</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>DEMO One</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>in-person</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>AV C141</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
         </is>
@@ -3030,7 +3048,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>AV C144; AV C141; Scott Engineering</t>
+          <t>AV C144; AV C141; Scott Engineering; Online</t>
         </is>
       </c>
     </row>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -162,11 +162,6 @@
     <author>migration</author>
   </authors>
   <commentList>
-    <comment ref="C5" authorId="0" shapeId="0">
-      <text>
-        <t>Guessed during the migration from the old schedules, because the grid only gave a first name or a title. Please confirm and clear the highlight. See MIGRATION-NOTES.md.</t>
-      </text>
-    </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
         <t>Guessed during the migration from the old schedules, because the grid only gave a first name or a title. Please confirm and clear the highlight. See MIGRATION-NOTES.md.</t>
@@ -595,9 +590,9 @@
           <t>Ben</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>gtf</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>faculty</t>
         </is>
       </c>
     </row>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1073,54 +1073,6 @@
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>gtf</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>DEMO One</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>DEMO - example (AV 141)</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>faculty</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>DEMO Two</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>DEMO - example (Scott)</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>la</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2669,123 +2621,6 @@
       <c r="D66" s="4" t="inlineStr">
         <is>
           <t>10:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>DEMO One</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>6:30 PM</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>in-person</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>AV C141</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>DEMO Two</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>in-person</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Scott Engineering</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>DEMO One</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>in-person</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>AV C141</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>DEMO ROW - delete this person and their shifts before students use the site.</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3056,6 +2891,18 @@
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>ENGR 111 -&gt; ENGR 123</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>buildings</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>AV -&gt; Academic Village</t>
         </is>
       </c>
     </row>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -514,6 +514,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -547,6 +548,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>courses_tutoring</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,6 +565,16 @@
           <t>la</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Also tutors in Spanish.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; CHEM 113; CHEM 114; CHEM 120; CHEM 121; PH 141; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -571,6 +587,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; Precalculus; MATH 160; MATH 161</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -583,6 +604,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; Precalculus; MATH 160; MATH 161</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -607,6 +633,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PH 141; Precalculus; MATH 160; CS 150B; ENGR 114; LIFE 102</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -679,6 +710,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; PH 141; Precalculus; MATH 160; CIVE 260; ENGR 111</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -703,6 +739,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; CHEM 113; CHEM 114; CHEM 120; CHEM 121; CHEM 341; CHEM 343; PH 141; Precalculus; MATH 160; LIFE 102</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -715,6 +756,16 @@
           <t>la</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Also tutors in Spanish.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PH 141; MATH 160; MATH 161</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -727,6 +778,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Precalculus; MATH 160; MATH 261</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -739,6 +795,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PH 141; Precalculus; MATH 160; CIVE 261; CIVE 260; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -775,6 +836,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; CHEM 113; CHEM 114; CHEM 120; CHEM 121; PH 141; PH 142; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CIVE 261; CIVE 360; CIVE 260; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -787,6 +853,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>PH 141; Precalculus; MATH 160; CIVE 261; CIVE 360; CIVE 260</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -799,6 +870,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; CHEM 113; CHEM 114; PH 141; PH 142; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CIVE 260; ENGR 111; ENGR 114; LIFE 102</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -811,6 +887,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; MATH 160; CIVE 360; CIVE 260; ENGR 111</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -835,6 +916,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CHEM 120; CHEM 121; MATH 161</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -847,6 +933,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; Precalculus; MATH 160; MATH 161; LIFE 102</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -859,6 +950,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; PH 141; PH 142; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CS 150A; CS 150B; CS 164; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -895,6 +991,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; CIVE 360; CIVE 260; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -907,6 +1008,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Precalculus; MATH 160; CIVE 360; CIVE 260; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -931,6 +1037,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; CHEM 113; CHEM 114; CHEM 120; CHEM 121; Precalculus; MATH 160; MATH 261; LIFE 102</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -943,6 +1054,16 @@
           <t>la</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Also tutors in Bengali.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>PH 141; PH 142; Precalculus; MATH 160; MATH 161; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -955,6 +1076,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>MATH 160; MATH 161; MATH 261; MATH 340; CIVE 261; CIVE 360; CIVE 260; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -967,6 +1093,16 @@
           <t>la</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Also tutors in Spanish.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; CHEM 113; CHEM 114; PH 141; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CIVE 261; CIVE 360; CIVE 260; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1003,6 +1139,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; PH 141; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CS 150A; CS 150B; CS 164; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1027,6 +1168,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; Precalculus; MATH 160; MATH 261; MATH 340; CIVE 261; CIVE 360; CIVE 260; ENGR 111</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1039,6 +1185,16 @@
           <t>la</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Also tutors in Hungarian.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CHEM 120; CHEM 121; CHEM 341; PH 141; Precalculus; MATH 160</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1063,6 +1219,11 @@
           <t>la</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; Precalculus; MATH 160; MATH 161; MATH 340; LIFE 102</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1076,10 +1237,70 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Christine Parkin</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>tutor</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CHEM 111; CHEM 112; PH 141; Precalculus; MATH 160; CS 150A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ethan Kennel</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>tutor</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PH 141; PH 142; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CIVE 261; CIVE 360; CIVE 260</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Tom Brown</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>tutor</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Izobel M</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>tutor</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Role must be faculty, gtf, or la." type="list">
-      <formula1>"faculty,gtf,la"</formula1>
+    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Role must be faculty, gtf, la, or tutor." type="list">
+      <formula1>"faculty,gtf,la,tutor"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1093,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1105,6 +1326,7 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1153,6 +1375,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>program</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2624,11 +2851,1979 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ariana Wright</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jordy Medina Valverde</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Safwan Ahmad</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jordy Medina Valverde</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Joseph Ramirez</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Landon Gagliostro</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Jady Sharp</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Jordy Medina Valverde</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Maisy Shull</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Jady Sharp</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Lauren Watts</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Safwan Ahmad</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Angel Tinoco</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Jady Sharp</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Lauren Watts</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Logan Rosebrock</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Angel Tinoco</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ethan Kennel</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Logan Rosebrock</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Austin Monroe</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mia Schulze</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Thomas Miller</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Austin Monroe</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Hannah Gruber</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Mia Schulze</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Austin Monroe</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Hannah Gruber</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sarah Goudjil</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Christine Parkin</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sarah Goudjil</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sylvia Ingegneri</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Caleb Adams</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Christine Parkin</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sarah Goudjil</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sylvia Ingegneri</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Caleb Adams</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sarah Goudjil</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Ariana Wright</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Joseph Quiroz Hernandez</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Logan Rosebrock</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Joseph Quiroz Hernandez</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Joseph Ramirez</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Owen Myers</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Tia Fountain</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Safwan Ahmad</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sofia Hiller</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Tia Fountain</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sofia Hiller</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sylvia Ingegneri</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sarah Goudjil</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sofia Hiller</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Ethan Kennel</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sofia Hiller</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Landon Gagliostro</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Lauren Watts</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Thomas Miller</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Lauren Watts</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Tucker Cullen</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Christine Parkin</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Christine Parkin</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Kael Spry</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Christine Parkin</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Kael Spry</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Tucker Cullen</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ethan Kennel</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Kael Spry</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Mia White</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Tucker Cullen</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Ethan Kennel</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Mia White</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>River Wysock</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>River Wysock</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>River Wysock</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="B2:B400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Office hours are Monday to Friday." type="list">
-      <formula1>"Monday,Tuesday,Wednesday,Thursday,Friday"</formula1>
-    </dataValidation>
+  <dataValidations count="5">
     <dataValidation sqref="E2:E400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Use in-person or online. Blank means in-person." type="list">
       <formula1>"in-person,online"</formula1>
     </dataValidation>
@@ -2637,6 +4832,12 @@
     </dataValidation>
     <dataValidation sqref="A2:A400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Pick a name from the people sheet. Add them there first if they are new." type="list">
       <formula1>PeopleNames</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Use office hours or tutoring. Blank means office hours." type="list">
+      <formula1>"office hours,tutoring"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Pick a day of the week." type="list">
+      <formula1>"Monday,Tuesday,Wednesday,Thursday,Friday,Saturday,Sunday"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2723,7 +4924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2903,6 +5104,66 @@
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>AV -&gt; Academic Village</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>default_program</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>office hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>program_order</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>office hours; tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>default_location_tutoring</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>AV C141</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>subjects</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ENGR -&gt; Engineering; MATH -&gt; Math; Precalculus -&gt; Math; CHEM -&gt; Chemistry; PH -&gt; Physics; CIVE -&gt; Civil Engineering; CS -&gt; Computer Science; LIFE -&gt; Biology</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>course_order</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ENGR 111; ENGR 114; ENGR 123; CHEM 111; CHEM 112; CHEM 113; CHEM 114; CHEM 120; CHEM 121; CHEM 341; CHEM 343; PH 141; PH 142; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CIVE 260; CIVE 261; CIVE 360; CS 150A; CS 150B; CS 164; LIFE 102</t>
         </is>
       </c>
     </row>
@@ -2917,7 +5178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2930,6 +5191,9 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2944,155 +5208,309 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>people sheet - everyone who holds office hours, listed once</t>
+          <t>The workbook covers two things: ENGR office hours, and tutoring in AV C141.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  name          the exact name used on the shifts sheet. Must be unique.</t>
+          <t>A person can do both - they are listed once and get a row per shift either way.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  display_name  what students see, if different (e.g. Dr. Torres). Blank = same as name.</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  role          faculty, gtf, or la. Pick from the dropdown.</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>people sheet - everyone who holds hours, listed once</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  courses       leave BLANK if they help with the default (ENGR 111 and ENGR 114).</t>
+          <t xml:space="preserve">  name          the exact name used on the shifts sheet. Must be unique.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">                If you fill it in, list ALL courses they cover, separated by ;</t>
+          <t xml:space="preserve">  display_name  what students see, if different (e.g. Dr. Torres). Blank = same as name.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  email, notes  optional. Both are shown to students, so keep notes short and useful.</t>
+          <t xml:space="preserve">  role          faculty, gtf, la, or tutor. Pick from the dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Use tutor only for someone who tutors and is not also an LA.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Yellow cells were guessed during the migration - please check them.</t>
+          <t xml:space="preserve">  courses       what they help with at ENGR OFFICE HOURS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Leave BLANK for the default (ENGR 111 and ENGR 114).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>shifts sheet - one row per weekly office hour</t>
+          <t xml:space="preserve">                If you fill it in, list ALL courses they cover, separated by ;</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  name          pick from the dropdown (it reads the people sheet)</t>
+          <t xml:space="preserve">                Anyone covering ENGR 111 is counted for ENGR 123 too - see the</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  day           Monday through Friday</t>
+          <t xml:space="preserve">                course_implies row on the settings sheet.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  start / end   like 9:00 AM or 1:30 PM. Must land on the hour or half hour.</t>
+          <t xml:space="preserve">  courses_tutoring   what they can help with AT TUTORING. Separated by ;</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mode          in-person or online. Blank = in-person.</t>
+          <t xml:space="preserve">                Blank means they do not tutor. This is the only place to edit it -</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  location      blank = the default room for their role (see settings).</t>
+          <t xml:space="preserve">                every one of their tutoring shifts reads from this cell.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">                For online, put the meeting link here.</t>
+          <t xml:space="preserve">  email, notes  optional. Both are shown to students, so keep notes short and useful.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  active        put no to hide a row for a while without deleting it.</t>
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Yellow cells were guessed during the migration - please check them.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>exceptions sheet - one-off changes to the normal week</t>
-        </is>
-      </c>
+      <c r="A25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cancel one shift:  name, date, start, end, type = cancelled</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>shifts sheet - one row per weekly hour</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cancel a whole day for someone: leave start and end blank</t>
+          <t xml:space="preserve">  name          pick from the dropdown (it reads the people sheet)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Add extra hours:   name, date, start, end, type = added</t>
+          <t xml:space="preserve">  day           Monday through Sunday. Days with no rows show as closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  start / end   like 9:00 AM or 1:30 PM. Must land on the hour or half hour.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>settings sheet - term dates, default rooms, and the announcement banner</t>
+          <t xml:space="preserve">  program       office hours or tutoring. Blank = office hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Tutoring rows take their room and their courses from tutoring:</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                leave location and courses blank unless this one row differs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mode          in-person or online. Blank = in-person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  location      blank = the default room for the programme (see settings).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Fill it in for anywhere else - Scott Engineering, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                The site gives every room its own colour automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                For online, put the meeting link here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  courses       blank = whatever the people sheet says for that programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  active        put no to hide a row for a while without deleting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>exceptions sheet - one-off changes to the normal week</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cancel one shift:  name, date, start, end, type = cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cancel a whole day for someone: leave start and end blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Add extra hours:   name, date, start, end, type = added</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>settings sheet - term dates, default rooms, and the announcement banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  default_location_tutoring   the tutoring room. One edit moves the whole</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  subjects                    groups the courses in the Get help with menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  course_order                the order that menu lists them in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>When you are done: save, then send the file to Ben (or save it back to OneDrive).</t>
         </is>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -160,6 +160,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>migration</author>
+    <author>faculty grid</author>
   </authors>
   <commentList>
     <comment ref="C7" authorId="0" shapeId="0">
@@ -210,6 +211,11 @@
     <comment ref="C45" authorId="0" shapeId="0">
       <text>
         <t>Guessed during the migration from the old schedules, because the grid only gave a first name or a title. Please confirm and clear the highlight. See MIGRATION-NOTES.md.</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="1" shapeId="0">
+      <text>
+        <t>Guessed when this name arrived on the Faculty &amp; GTF grid, which only gave a first name or a title. Please confirm and clear the highlight. See HANDOFF.md.</t>
       </text>
     </comment>
   </commentList>
@@ -505,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1282,7 +1288,6 @@
           <t>tutor</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1295,7 +1300,18 @@
           <t>tutor</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Leila</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>gtf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1314,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1384,7 +1400,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>DrT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1406,7 +1422,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DrT</t>
+          <t>Logan Rosebrock</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1428,7 +1444,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Logan Rosebrock</t>
+          <t>Safwan Ahmad</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1438,19 +1454,19 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Dr. Dan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1460,19 +1476,19 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Safwan Ahmad</t>
+          <t>Lydia Iliev</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1482,19 +1498,19 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dr. Dan</t>
+          <t>Ariana Wright</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1504,19 +1520,19 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lydia Iliev</t>
+          <t>Dr. Harvey</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1526,19 +1542,19 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ariana Wright</t>
+          <t>Kael Spry</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1548,19 +1564,19 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dr. Harvey</t>
+          <t>Leila</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1570,19 +1586,19 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kael Spry</t>
+          <t>Leila</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1592,12 +1608,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1643,7 @@
           <t>online</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://teams.microsoft.com/meet/245625331850941?p=iV1rimtH5TCpcr9fc3</t>
         </is>
@@ -1768,7 +1784,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dr. Yume</t>
+          <t>Leila</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1778,19 +1794,19 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>12:00 PM</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>1:00 PM</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Joseph Ramirez</t>
+          <t>Dr. Yume</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1812,7 +1828,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dr. Yume</t>
+          <t>Joseph Ramirez</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1822,19 +1838,19 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>2:00 PM</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mia Schulze</t>
+          <t>Dr. Yume</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1856,7 +1872,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Prof Scheller</t>
+          <t>Mia Schulze</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1878,7 +1894,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sophie DeMatteo</t>
+          <t>Prof Scheller</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1888,29 +1904,19 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
           <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>https://teams.microsoft.com/meet/235485688487049?p=yJrCzr8Ds8hzdA8dh2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1920,19 +1926,19 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Sophie DeMatteo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1942,85 +1948,95 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/meet/235485688487049?p=yJrCzr8Ds8hzdA8dh2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Owen Myers</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kacey Hoang</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dr. Dan</t>
+          <t>Jordy Medina Valverde</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2030,19 +2046,19 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lauren Watts</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2052,19 +2068,19 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Winnie</t>
+          <t>Owen Myers</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2074,19 +2090,19 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dr. Yume</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2096,19 +2112,19 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>River Wysock</t>
+          <t>Kacey Hoang</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2118,19 +2134,19 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DrT</t>
+          <t>Dr. Dan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2140,19 +2156,19 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Joseph Quiroz Hernandez</t>
+          <t>Lauren Watts</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2162,19 +2178,19 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Winnie</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2184,19 +2200,19 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DrT</t>
+          <t>Dr. Yume</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2206,19 +2222,19 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hannah Gruber</t>
+          <t>River Wysock</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2228,19 +2244,19 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sumaiya</t>
+          <t>DrT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2250,19 +2266,19 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jordy Medina Valverde</t>
+          <t>Joseph Quiroz Hernandez</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2272,85 +2288,85 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Parker Bjick</t>
+          <t>DrT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Hannah Gruber</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Austin Monroe</t>
+          <t>Sumaiya</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Sylvia Ingegneri</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2360,19 +2376,19 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Parker Bjick</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2382,19 +2398,19 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tia Fountain</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2404,19 +2420,19 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dr. Harvey</t>
+          <t>Austin Monroe</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2426,19 +2442,19 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sarah Goudjil</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2448,19 +2464,19 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dr. Harvey</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2470,19 +2486,19 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Prof Scheller</t>
+          <t>Tia Fountain</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2492,19 +2508,19 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tucker Cullen</t>
+          <t>Dr. Harvey</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2514,29 +2530,19 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
           <t>2:00 PM</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>https://teams.microsoft.com/l/message/19:42625ed077084999881c0275e689deec@thread.v2/1787625651798?context=%7B%22contextType%22%3A%22chat%22%7D</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Julie Rickerd</t>
+          <t>Sarah Goudjil</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2546,19 +2552,19 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Prof Scheller</t>
+          <t>Dr. Harvey</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2568,19 +2574,19 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
           <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Prof Scheller</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2590,19 +2596,19 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Tucker Cullen</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2612,19 +2618,29 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/l/message/19:42625ed077084999881c0275e689deec@thread.v2/1787625651798?context=%7B%22contextType%22%3A%22chat%22%7D</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sylvia Ingegneri</t>
+          <t>Julie Rickerd</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2634,85 +2650,85 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mia White</t>
+          <t>Prof Scheller</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Winnie</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jady Sharp</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Caleb Adams</t>
+          <t>Thomas Miller</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2722,19 +2738,19 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Winnie</t>
+          <t>Mia White</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2744,19 +2760,19 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Landon Gagliostro</t>
+          <t>Winnie</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2766,19 +2782,19 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Olivia Kalinowski</t>
+          <t>Jady Sharp</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2788,29 +2804,19 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>https://teams.microsoft.com/l/message/19:42625ed077084999881c0275e689deec@thread.v2/1787623810109?context=%7B%22contextType%22%3A%22chat%22%7D</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tito Salcido Rascon</t>
+          <t>Caleb Adams</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2820,19 +2826,19 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Thomas Miller</t>
+          <t>Winnie</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2842,78 +2848,78 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ariana Wright</t>
+          <t>Landon Gagliostro</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>tutoring</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jordy Medina Valverde</t>
+          <t>Olivia Kalinowski</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>tutoring</t>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/l/message/19:42625ed077084999881c0275e689deec@thread.v2/1787623810109?context=%7B%22contextType%22%3A%22chat%22%7D</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Safwan Ahmad</t>
+          <t>Tito Salcido Rascon</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2924,18 +2930,13 @@
       <c r="D69" s="4" t="inlineStr">
         <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>tutoring</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jordy Medina Valverde</t>
+          <t>Ariana Wright</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2945,12 +2946,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -2962,7 +2963,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Joseph Ramirez</t>
+          <t>Jordy Medina Valverde</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2972,12 +2973,12 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -2989,7 +2990,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Landon Gagliostro</t>
+          <t>Safwan Ahmad</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2999,12 +3000,12 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3016,7 +3017,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jady Sharp</t>
+          <t>Jordy Medina Valverde</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3026,12 +3027,12 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3043,7 +3044,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jordy Medina Valverde</t>
+          <t>Joseph Ramirez</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3053,12 +3054,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3070,7 +3071,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Maisy Shull</t>
+          <t>Landon Gagliostro</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3080,12 +3081,12 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3107,12 +3108,12 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -3124,7 +3125,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lauren Watts</t>
+          <t>Jordy Medina Valverde</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3134,12 +3135,12 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3151,7 +3152,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Safwan Ahmad</t>
+          <t>Maisy Shull</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3161,12 +3162,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -3178,7 +3179,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Angel Tinoco</t>
+          <t>Jady Sharp</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3188,12 +3189,12 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -3205,7 +3206,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Jady Sharp</t>
+          <t>Lauren Watts</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3215,12 +3216,12 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -3232,7 +3233,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lauren Watts</t>
+          <t>Safwan Ahmad</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3242,12 +3243,12 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -3259,7 +3260,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Logan Rosebrock</t>
+          <t>Angel Tinoco</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3286,7 +3287,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Angel Tinoco</t>
+          <t>Jady Sharp</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3296,12 +3297,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
           <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -3313,7 +3314,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ethan Kennel</t>
+          <t>Lauren Watts</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3323,12 +3324,12 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
           <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -3350,12 +3351,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
           <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -3367,22 +3368,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Austin Monroe</t>
+          <t>Angel Tinoco</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -3394,22 +3395,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mia Schulze</t>
+          <t>Ethan Kennel</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -3421,22 +3422,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Thomas Miller</t>
+          <t>Logan Rosebrock</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -3458,12 +3459,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -3475,7 +3476,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hannah Gruber</t>
+          <t>Mia Schulze</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3485,12 +3486,12 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -3502,7 +3503,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mia Schulze</t>
+          <t>Thomas Miller</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3512,12 +3513,12 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -3539,12 +3540,12 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -3566,12 +3567,12 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -3583,7 +3584,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sarah Goudjil</t>
+          <t>Mia Schulze</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3593,12 +3594,12 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -3610,7 +3611,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Christine Parkin</t>
+          <t>Austin Monroe</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3620,12 +3621,12 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -3637,7 +3638,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sarah Goudjil</t>
+          <t>Hannah Gruber</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3647,12 +3648,12 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -3664,7 +3665,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sylvia Ingegneri</t>
+          <t>Sarah Goudjil</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3674,12 +3675,12 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -3691,7 +3692,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Caleb Adams</t>
+          <t>Christine Parkin</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3701,12 +3702,12 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -3718,7 +3719,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Christine Parkin</t>
+          <t>Sarah Goudjil</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3728,12 +3729,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -3745,7 +3746,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sarah Goudjil</t>
+          <t>Sylvia Ingegneri</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3755,12 +3756,12 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -3772,7 +3773,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sylvia Ingegneri</t>
+          <t>Caleb Adams</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3799,7 +3800,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Caleb Adams</t>
+          <t>Christine Parkin</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3809,12 +3810,12 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
           <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D102" s="4" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -3836,12 +3837,12 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
           <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -3853,22 +3854,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ariana Wright</t>
+          <t>Sylvia Ingegneri</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -3880,22 +3881,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Joseph Quiroz Hernandez</t>
+          <t>Caleb Adams</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -3907,22 +3908,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Logan Rosebrock</t>
+          <t>Sarah Goudjil</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -3934,7 +3935,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Joseph Quiroz Hernandez</t>
+          <t>Ariana Wright</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3944,12 +3945,12 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -3961,7 +3962,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Joseph Ramirez</t>
+          <t>Joseph Quiroz Hernandez</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3971,12 +3972,12 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -3988,7 +3989,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Owen Myers</t>
+          <t>Logan Rosebrock</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3998,12 +3999,12 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -4015,7 +4016,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Tia Fountain</t>
+          <t>Joseph Quiroz Hernandez</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4042,7 +4043,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Safwan Ahmad</t>
+          <t>Joseph Ramirez</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4052,12 +4053,12 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -4069,7 +4070,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sofia Hiller</t>
+          <t>Owen Myers</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4079,12 +4080,12 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -4106,12 +4107,12 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -4123,7 +4124,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sofia Hiller</t>
+          <t>Safwan Ahmad</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4133,12 +4134,12 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D114" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -4150,7 +4151,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sylvia Ingegneri</t>
+          <t>Sofia Hiller</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4160,12 +4161,12 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -4177,7 +4178,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sarah Goudjil</t>
+          <t>Tia Fountain</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4187,12 +4188,12 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -4214,12 +4215,12 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -4231,7 +4232,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ethan Kennel</t>
+          <t>Sylvia Ingegneri</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4241,12 +4242,12 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>8:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>9:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -4258,7 +4259,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sofia Hiller</t>
+          <t>Sarah Goudjil</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4268,12 +4269,12 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
           <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -4285,22 +4286,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Landon Gagliostro</t>
+          <t>Sofia Hiller</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -4312,22 +4313,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lauren Watts</t>
+          <t>Ethan Kennel</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -4339,22 +4340,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Thomas Miller</t>
+          <t>Sofia Hiller</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -4366,7 +4367,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Lauren Watts</t>
+          <t>Landon Gagliostro</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4376,12 +4377,12 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -4393,7 +4394,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tucker Cullen</t>
+          <t>Lauren Watts</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4403,12 +4404,12 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
+          <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
           <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>5:00 PM</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -4420,7 +4421,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Christine Parkin</t>
+          <t>Thomas Miller</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4430,12 +4431,12 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -4447,7 +4448,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Christine Parkin</t>
+          <t>Lauren Watts</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4457,12 +4458,12 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -4474,7 +4475,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kael Spry</t>
+          <t>Tucker Cullen</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4484,12 +4485,12 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
           <t>5:00 PM</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -4511,12 +4512,12 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -4528,7 +4529,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Kael Spry</t>
+          <t>Christine Parkin</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4538,12 +4539,12 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -4555,7 +4556,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Tucker Cullen</t>
+          <t>Kael Spry</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4565,12 +4566,12 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
           <t>6:00 PM</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -4582,7 +4583,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ethan Kennel</t>
+          <t>Christine Parkin</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4592,12 +4593,12 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -4619,12 +4620,12 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -4636,7 +4637,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Mia White</t>
+          <t>Tucker Cullen</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4646,12 +4647,12 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -4663,7 +4664,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Tucker Cullen</t>
+          <t>Ethan Kennel</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4690,7 +4691,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ethan Kennel</t>
+          <t>Kael Spry</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4700,12 +4701,12 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
           <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -4727,12 +4728,12 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
           <t>8:00 PM</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -4744,22 +4745,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>River Wysock</t>
+          <t>Tucker Cullen</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -4771,22 +4772,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>River Wysock</t>
+          <t>Ethan Kennel</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -4798,25 +4799,106 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Mia White</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>8:00 PM</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>9:00 PM</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>River Wysock</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>5:00 PM</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>River Wysock</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>6:00 PM</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
         <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>tutoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>River Wysock</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>7:00 PM</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>8:00 PM</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J142" t="inlineStr">
         <is>
           <t>tutoring</t>
         </is>
@@ -5191,9 +5273,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -5208,9 +5288,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -5225,9 +5303,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -5326,9 +5402,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -5437,9 +5511,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
@@ -5468,9 +5540,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
@@ -5506,9 +5576,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>tutor</t>
+          <t>la</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>tutor</t>
+          <t>la</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tutor</t>
+          <t>la</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>tutor</t>
+          <t>la</t>
         </is>
       </c>
     </row>
@@ -1315,8 +1315,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Role must be faculty, gtf, la, or tutor." type="list">
-      <formula1>"faculty,gtf,la,tutor"</formula1>
+    <dataValidation sqref="C2:C400" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Role must be faculty, gtf, or la." type="list">
+      <formula1>"faculty,gtf,la"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5260,7 +5260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -5273,7 +5273,9 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -5288,7 +5290,9 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -5303,7 +5307,9 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -5328,257 +5334,272 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  role          faculty, gtf, la, or tutor. Pick from the dropdown.</t>
+          <t xml:space="preserve">  role          faculty, gtf, or la. Pick from the dropdown.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Use tutor only for someone who tutors and is not also an LA.</t>
+          <t xml:space="preserve">                Everyone who tutors is an la, whether or not they also hold</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  courses       what they help with at ENGR OFFICE HOURS.</t>
+          <t xml:space="preserve">                ENGR office hours.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Leave BLANK for the default (ENGR 111 and ENGR 114).</t>
+          <t xml:space="preserve">  courses       what they help with at ENGR OFFICE HOURS.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                If you fill it in, list ALL courses they cover, separated by ;</t>
+          <t xml:space="preserve">                Leave BLANK for the default (ENGR 111 and ENGR 114).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Anyone covering ENGR 111 is counted for ENGR 123 too - see the</t>
+          <t xml:space="preserve">                If you fill it in, list ALL courses they cover, separated by ;</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">                course_implies row on the settings sheet.</t>
+          <t xml:space="preserve">                Anyone covering ENGR 111 is counted for ENGR 123 too - see the</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  courses_tutoring   what they can help with AT TUTORING. Separated by ;</t>
+          <t xml:space="preserve">                course_implies row on the settings sheet.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Blank means they do not tutor. This is the only place to edit it -</t>
+          <t xml:space="preserve">  courses_tutoring   what they can help with AT TUTORING. Separated by ;</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">                every one of their tutoring shifts reads from this cell.</t>
+          <t xml:space="preserve">                Blank means they do not tutor. This is the only place to edit it -</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">                every one of their tutoring shifts reads from this cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">  email, notes  optional. Both are shown to students, so keep notes short and useful.</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  Yellow cells were guessed during the migration - please check them.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>shifts sheet - one row per weekly hour</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  name          pick from the dropdown (it reads the people sheet)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  day           Monday through Sunday. Days with no rows show as closed.</t>
+          <t xml:space="preserve">  name          pick from the dropdown (it reads the people sheet)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  start / end   like 9:00 AM or 1:30 PM. Must land on the hour or half hour.</t>
+          <t xml:space="preserve">  day           Monday through Sunday. Days with no rows show as closed.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  program       office hours or tutoring. Blank = office hours.</t>
+          <t xml:space="preserve">  start / end   like 9:00 AM or 1:30 PM. Must land on the hour or half hour.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Tutoring rows take their room and their courses from tutoring:</t>
+          <t xml:space="preserve">  program       office hours or tutoring. Blank = office hours.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">                leave location and courses blank unless this one row differs.</t>
+          <t xml:space="preserve">                Tutoring rows take their room and their courses from tutoring:</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mode          in-person or online. Blank = in-person.</t>
+          <t xml:space="preserve">                leave location and courses blank unless this one row differs.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  location      blank = the default room for the programme (see settings).</t>
+          <t xml:space="preserve">  mode          in-person or online. Blank = in-person.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Fill it in for anywhere else - Scott Engineering, etc.</t>
+          <t xml:space="preserve">  location      blank = the default room for the programme (see settings).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">                The site gives every room its own colour automatically.</t>
+          <t xml:space="preserve">                Fill it in for anywhere else - Scott Engineering, etc.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">                For online, put the meeting link here.</t>
+          <t xml:space="preserve">                The site gives every room its own colour automatically.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  courses       blank = whatever the people sheet says for that programme.</t>
+          <t xml:space="preserve">                For online, put the meeting link here.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t xml:space="preserve">  courses       blank = whatever the people sheet says for that programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t xml:space="preserve">  active        put no to hide a row for a while without deleting it.</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>exceptions sheet - one-off changes to the normal week</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cancel one shift:  name, date, start, end, type = cancelled</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cancel a whole day for someone: leave start and end blank</t>
+          <t xml:space="preserve">  Cancel one shift:  name, date, start, end, type = cancelled</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Cancel a whole day for someone: leave start and end blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Add extra hours:   name, date, start, end, type = added</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>settings sheet - term dates, default rooms, and the announcement banner</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  default_location_tutoring   the tutoring room. One edit moves the whole</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">                              programme.</t>
+          <t xml:space="preserve">  default_location_tutoring   the tutoring room. One edit moves the whole</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  subjects                    groups the courses in the Get help with menu.</t>
+          <t xml:space="preserve">                              programme.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t xml:space="preserve">  subjects                    groups the courses in the Get help with menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t xml:space="preserve">  course_order                the order that menu lists them in.</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>When you are done: save, then send the file to Ben (or save it back to OneDrive).</t>
         </is>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -521,6 +521,7 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -559,6 +560,11 @@
           <t>courses_tutoring</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>languages</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -571,14 +577,14 @@
           <t>la</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Also tutors in Spanish.</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>CHEM 111; CHEM 112; CHEM 113; CHEM 114; CHEM 120; CHEM 121; PH 141; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -762,14 +768,14 @@
           <t>la</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Also tutors in Spanish.</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>PH 141; MATH 160; MATH 161</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1060,14 +1066,14 @@
           <t>la</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Also tutors in Bengali.</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>PH 141; PH 142; Precalculus; MATH 160; MATH 161; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bengali</t>
         </is>
       </c>
     </row>
@@ -1099,14 +1105,14 @@
           <t>la</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Also tutors in Spanish.</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>CHEM 111; CHEM 112; CHEM 113; CHEM 114; PH 141; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CIVE 261; CIVE 360; CIVE 260; ENGR 111; ENGR 114</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1197,14 @@
           <t>la</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Also tutors in Hungarian.</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>CHEM 120; CHEM 121; CHEM 341; PH 141; Precalculus; MATH 160</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Hungarian</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -5273,9 +5279,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -5290,9 +5294,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -5307,9 +5309,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -5411,195 +5411,208 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  email, notes  optional. Both are shown to students, so keep notes short and useful.</t>
+          <t xml:space="preserve">  languages     languages BESIDES ENGLISH they can help in, separated by ;</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                Blank for most people. Becomes the Language filter and a</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Yellow cells were guessed during the migration - please check them.</t>
+          <t xml:space="preserve">                line in the panel. Rebuilt from the rota's bilingual list.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr"/>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  email, notes  optional. Both are shown to students, so keep notes short and useful.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>shifts sheet - one row per weekly hour</t>
-        </is>
-      </c>
+      <c r="A27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  name          pick from the dropdown (it reads the people sheet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  day           Monday through Sunday. Days with no rows show as closed.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  Yellow cells were guessed during the migration - please check them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  start / end   like 9:00 AM or 1:30 PM. Must land on the hour or half hour.</t>
+          <t>shifts sheet - one row per weekly hour</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  program       office hours or tutoring. Blank = office hours.</t>
+          <t xml:space="preserve">  name          pick from the dropdown (it reads the people sheet)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Tutoring rows take their room and their courses from tutoring:</t>
+          <t xml:space="preserve">  day           Monday through Sunday. Days with no rows show as closed.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">                leave location and courses blank unless this one row differs.</t>
+          <t xml:space="preserve">  start / end   like 9:00 AM or 1:30 PM. Must land on the hour or half hour.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  mode          in-person or online. Blank = in-person.</t>
+          <t xml:space="preserve">  program       office hours or tutoring. Blank = office hours.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  location      blank = the default room for the programme (see settings).</t>
+          <t xml:space="preserve">                Tutoring rows take their room and their courses from tutoring:</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">                Fill it in for anywhere else - Scott Engineering, etc.</t>
+          <t xml:space="preserve">                leave location and courses blank unless this one row differs.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">                The site gives every room its own colour automatically.</t>
+          <t xml:space="preserve">  mode          in-person or online. Blank = in-person.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">                For online, put the meeting link here.</t>
+          <t xml:space="preserve">  location      blank = the default room for the programme (see settings).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  courses       blank = whatever the people sheet says for that programme.</t>
+          <t xml:space="preserve">                Fill it in for anywhere else - Scott Engineering, etc.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  active        put no to hide a row for a while without deleting it.</t>
+          <t xml:space="preserve">                The site gives every room its own colour automatically.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                For online, put the meeting link here.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>exceptions sheet - one-off changes to the normal week</t>
+          <t xml:space="preserve">  courses       blank = whatever the people sheet says for that programme.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t xml:space="preserve">  active        put no to hide a row for a while without deleting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>exceptions sheet - one-off changes to the normal week</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Cancel one shift:  name, date, start, end, type = cancelled</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cancel a whole day for someone: leave start and end blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Add extra hours:   name, date, start, end, type = added</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>settings sheet - term dates, default rooms, and the announcement banner</t>
+          <t xml:space="preserve">  Cancel a whole day for someone: leave start and end blank</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  default_location_tutoring   the tutoring room. One edit moves the whole</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                              programme.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  Add extra hours:   name, date, start, end, type = added</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  subjects                    groups the courses in the Get help with menu.</t>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>settings sheet - term dates, default rooms, and the announcement banner</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  course_order                the order that menu lists them in.</t>
+          <t xml:space="preserve">  default_location_tutoring   the tutoring room. One edit moves the whole</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              programme.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  subjects                    groups the courses in the Get help with menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  course_order                the order that menu lists them in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>When you are done: save, then send the file to Ben (or save it back to OneDrive).</t>
         </is>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -2196,7 +2196,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Winnie</t>
+          <t>Dr. Yume</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2206,19 +2206,19 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dr. Yume</t>
+          <t>River Wysock</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2240,7 +2240,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>River Wysock</t>
+          <t>DrT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2250,19 +2250,19 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DrT</t>
+          <t>Joseph Quiroz Hernandez</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2284,7 +2284,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Joseph Quiroz Hernandez</t>
+          <t>DrT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2294,19 +2294,19 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DrT</t>
+          <t>Hannah Gruber</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2328,7 +2328,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hannah Gruber</t>
+          <t>Sumaiya</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2338,41 +2338,41 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sumaiya</t>
+          <t>Sylvia Ingegneri</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sylvia Ingegneri</t>
+          <t>Parker Bjick</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2382,19 +2382,19 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Parker Bjick</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Austin Monroe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Austin Monroe</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2460,7 +2460,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2470,19 +2470,19 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Tia Fountain</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2504,7 +2504,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tia Fountain</t>
+          <t>Dr. Harvey</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dr. Harvey</t>
+          <t>Sarah Goudjil</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2548,7 +2548,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sarah Goudjil</t>
+          <t>Dr. Harvey</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2558,19 +2558,19 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dr. Harvey</t>
+          <t>Prof Scheller</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2592,7 +2592,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Prof Scheller</t>
+          <t>Tucker Cullen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2608,13 +2608,23 @@
       <c r="D55" s="4" t="inlineStr">
         <is>
           <t>3:00 PM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://teams.microsoft.com/l/message/19:42625ed077084999881c0275e689deec@thread.v2/1787625651798?context=%7B%22contextType%22%3A%22chat%22%7D</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tucker Cullen</t>
+          <t>Julie Rickerd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2624,29 +2634,19 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://teams.microsoft.com/l/message/19:42625ed077084999881c0275e689deec@thread.v2/1787625651798?context=%7B%22contextType%22%3A%22chat%22%7D</t>
+          <t>4:00 PM</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Julie Rickerd</t>
+          <t>Prof Scheller</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2668,7 +2668,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Prof Scheller</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
     </row>
@@ -2700,41 +2700,41 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ojo</t>
+          <t>Thomas Miller</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Thomas Miller</t>
+          <t>Winnie</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5279,7 +5279,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -5294,7 +5293,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -5309,7 +5307,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -5446,7 +5443,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
@@ -5545,7 +5541,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -5574,7 +5569,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
@@ -5610,7 +5604,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -620,7 +620,7 @@
     <t>course_order</t>
   </si>
   <si>
-    <t>ENGR 111; ENGR 114; ENGR 123; CHEM 111; CHEM 112; CHEM 113; CHEM 114; CHEM 120; CHEM 121; CHEM 341; CHEM 343; PH 141; PH 142; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CIVE 260; CIVE 261; CIVE 360; CS 150A; CS 150B; CS 164; LIFE 102</t>
+    <t>ENGR 111; ENGR 114; ENGR 123; Precalculus; MATH 160; MATH 161; MATH 261; MATH 340; CHEM 111; CHEM 112; CHEM 113; CHEM 114; CHEM 120; CHEM 121; CHEM 341; CHEM 343; PH 141; PH 142; CIVE 260; CIVE 261; CIVE 360; CS 150A; CS 150B; CS 164; LIFE 102</t>
   </si>
   <si>
     <t>default_location</t>

--- a/data/office-hours.xlsx
+++ b/data/office-hours.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bengrier/Desktop/CSU Work/AI App Creation/Office Hours Display/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0CF16D-2290-AC42-9B68-DC201CA51327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAEDD2F-EB34-5B40-B182-65870971DB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32020" yWindow="-3960" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="people" sheetId="1" r:id="rId1"/>
@@ -195,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="200">
   <si>
     <t>name</t>
   </si>
@@ -853,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -864,6 +864,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1697,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:E142"/>
@@ -1726,7 +1727,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1743,7 +1744,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1760,7 +1761,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -1777,7 +1778,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1794,7 +1795,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1811,7 +1812,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1828,7 +1829,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1845,7 +1846,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1862,7 +1863,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>84</v>
       </c>
@@ -1879,7 +1880,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1896,7 +1897,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -1913,7 +1914,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1930,7 +1931,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -1947,7 +1948,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -1964,7 +1965,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1981,7 +1982,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1998,7 +1999,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -2015,7 +2016,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -2032,7 +2033,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -2049,7 +2050,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2083,7 +2084,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -2100,7 +2101,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2117,7 +2118,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -2134,7 +2135,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -2151,7 +2152,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -2168,7 +2169,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2185,7 +2186,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>38</v>
       </c>
@@ -2202,7 +2203,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -2219,7 +2220,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -2236,7 +2237,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -2253,7 +2254,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2270,7 +2271,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -2287,7 +2288,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -2304,7 +2305,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2321,7 +2322,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -2338,7 +2339,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -2355,7 +2356,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -2372,7 +2373,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -2389,7 +2390,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -2406,7 +2407,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -2428,19 +2429,19 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C43" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" t="s">
-        <v>96</v>
+        <v>89</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0.5</v>
       </c>
       <c r="E43" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>10</v>
       </c>
@@ -2457,7 +2458,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2474,7 +2475,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -2491,7 +2492,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>64</v>
       </c>
@@ -2508,7 +2509,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>69</v>
       </c>
@@ -2525,7 +2526,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2542,7 +2543,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -2559,7 +2560,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -2576,7 +2577,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -2593,7 +2594,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>45</v>
       </c>
@@ -2610,7 +2611,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>10</v>
       </c>
@@ -2627,7 +2628,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -2644,7 +2645,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>21</v>
       </c>
@@ -2661,7 +2662,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -2678,7 +2679,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>78</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -2712,7 +2713,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>66</v>
       </c>
@@ -2729,7 +2730,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -2746,7 +2747,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>78</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>60</v>
       </c>
@@ -2780,7 +2781,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -2797,7 +2798,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -2814,7 +2815,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>60</v>
       </c>
@@ -2831,7 +2832,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>26</v>
       </c>
@@ -2848,7 +2849,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>15</v>
       </c>
@@ -2865,7 +2866,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>51</v>
       </c>
@@ -2882,7 +2883,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -2899,7 +2900,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>33</v>
       </c>
@@ -2916,7 +2917,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -2933,7 +2934,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>38</v>
       </c>
@@ -2950,7 +2951,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>19</v>
       </c>
@@ -2967,7 +2968,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>56</v>
       </c>
@@ -2984,7 +2985,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>20</v>
       </c>
@@ -3001,7 +3002,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -3018,7 +3019,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -3035,7 +3036,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>20</v>
       </c>
@@ -3052,7 +3053,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>21</v>
       </c>
@@ -3069,7 +3070,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>28</v>
       </c>
@@ -3086,7 +3087,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>28</v>
       </c>
@@ -3120,7 +3121,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -3137,7 +3138,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>51</v>
       </c>
@@ -3154,7 +3155,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>71</v>
       </c>
@@ -3171,7 +3172,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>57</v>
       </c>
@@ -3188,7 +3189,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>62</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>65</v>
       </c>
@@ -3222,7 +3223,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>71</v>
       </c>
@@ -3239,7 +3240,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>62</v>
       </c>
@@ -3256,7 +3257,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>66</v>
       </c>
@@ -3273,7 +3274,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>60</v>
       </c>
@@ -3290,7 +3291,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>62</v>
       </c>
@@ -3307,7 +3308,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>80</v>
       </c>
@@ -3324,7 +3325,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>62</v>
       </c>
@@ -3341,7 +3342,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>66</v>
       </c>
@@ -3358,7 +3359,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -3375,7 +3376,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>68</v>
       </c>
@@ -3392,7 +3393,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -3409,7 +3410,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>68</v>
       </c>
@@ -3426,7 +3427,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>49</v>
       </c>
@@ -3443,7 +3444,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>71</v>
       </c>
@@ -3460,7 +3461,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -3477,7 +3478,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>60</v>
       </c>
@@ -3494,7 +3495,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -3516,19 +3517,19 @@
         <v>55</v>
       </c>
       <c r="B107" t="s">
-        <v>109</v>
-      </c>
-      <c r="C107" t="s">
-        <v>95</v>
-      </c>
-      <c r="D107" t="s">
-        <v>96</v>
+        <v>107</v>
+      </c>
+      <c r="C107" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D107" s="6">
+        <v>0.70833333333333337</v>
       </c>
       <c r="E107" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>75</v>
       </c>
@@ -3545,7 +3546,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>32</v>
       </c>
@@ -3562,7 +3563,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>36</v>
       </c>
@@ -3579,7 +3580,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>38</v>
       </c>
@@ -3603,17 +3604,17 @@
       <c r="B112" t="s">
         <v>109</v>
       </c>
-      <c r="C112" t="s">
-        <v>96</v>
-      </c>
-      <c r="D112" t="s">
-        <v>97</v>
+      <c r="C112" s="6">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D112" s="6">
+        <v>0.64583333333333337</v>
       </c>
       <c r="E112" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>69</v>
       </c>
@@ -3630,7 +3631,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>38</v>
       </c>
@@ -3647,7 +3648,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>49</v>
       </c>
@@ -3664,7 +3665,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>75</v>
       </c>
@@ -3681,7 +3682,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>78</v>
       </c>
@@ -3698,7 +3699,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>78</v>
       </c>
@@ -3715,7 +3716,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>34</v>
       </c>
@@ -3732,7 +3733,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>49</v>
       </c>
@@ -3749,7 +3750,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>78</v>
       </c>
@@ -3766,7 +3767,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>34</v>
       </c>
@@ -3783,7 +3784,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>75</v>
       </c>
@@ -3800,7 +3801,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>80</v>
       </c>
@@ -3817,7 +3818,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>34</v>
       </c>
@@ -3834,7 +3835,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>47</v>
       </c>
@@ -3851,7 +3852,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>75</v>
       </c>
@@ -3868,7 +3869,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>80</v>
       </c>
@@ -3885,7 +3886,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>47</v>
       </c>
@@ -3902,7 +3903,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>69</v>
       </c>
@@ -3919,7 +3920,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>77</v>
       </c>
@@ -3936,7 +3937,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3953,7 +3954,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>77</v>
       </c>
@@ -3970,7 +3971,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>24</v>
       </c>
@@ -3987,7 +3988,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -4004,7 +4005,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>77</v>
       </c>
@@ -4021,7 +4022,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>36</v>
       </c>
@@ -4038,7 +4039,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>50</v>
       </c>
@@ -4055,7 +4056,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>74</v>
       </c>
@@ -4072,7 +4073,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>56</v>
       </c>
@@ -4089,7 +4090,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>56</v>
       </c>
@@ -4106,7 +4107,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>56</v>
       </c>
@@ -4124,7 +4125,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E142" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:E142" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Prof Scheller"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Check this cell" error="Pick a name from the people sheet. Add them there first if they are new." sqref="A2:A341" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>PeopleNames</formula1>
